--- a/deploy/src/main/resources/TRACK-TEMPLATE.xlsx
+++ b/deploy/src/main/resources/TRACK-TEMPLATE.xlsx
@@ -24,13 +24,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="冬青黑体简体中文 W3"/>
-        <charset val="134"/>
-      </rPr>
       <t>表头中带有“ 必填 ”的字段为必填项，请勿漏填，否则会导致埋点事件上传失败。</t>
     </r>
     <r>
@@ -103,7 +96,8 @@
 6.在填写“埋点平台”字段时，请严格按照示例1中所示枚举值填写，如该事件需要在安卓端和 iOS 端进行埋点，请填写：“Android/iOS”，除 Android、iOS、JavaScript、小程序、服务端之外，请填写“其他”。
 7.埋点所属环境，多选，选择项：测试环境、模拟环境、生产环境。若需要在多个环境埋点，请用“/”隔开。
 8.除了标注为可多选外，其他必填项都为单选。
-9.埋点位置说明 导入 产研系统埋点事件“埋点说明”字段。</t>
+9.埋点位置说明 导入 产研系统埋点事件“埋点说明”字段。
+10.对于带有“$”符号的属性为预置属性不可进行修改。</t>
     </r>
   </si>
   <si>
@@ -408,9 +402,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="35">
@@ -484,16 +478,16 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="DengXian"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="DengXian"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="DengXian"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -505,14 +499,53 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="DengXian"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="DengXian"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="DengXian"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="DengXian"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="DengXian"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="DengXian"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="DengXian"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -526,6 +559,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="DengXian"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -534,16 +575,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="DengXian"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
       <name val="DengXian"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -556,18 +596,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="DengXian"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="DengXian"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -587,29 +620,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="DengXian"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="DengXian"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="DengXian"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -618,14 +628,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="DengXian"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="DengXian"/>
@@ -633,14 +635,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="DengXian"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="冬青黑体简体中文 W3"/>
@@ -698,187 +692,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1116,6 +1110,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -1127,6 +1132,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1164,17 +1184,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1193,174 +1207,154 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="22" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="57">
